--- a/inst/extdata/text_elements/BT_Quellenangaben.xlsx
+++ b/inst/extdata/text_elements/BT_Quellenangaben.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alina\Desktop\IQB\BT-ShinyApp\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eat\BT-ShinyApp\inst\extdata\text_elements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2FBF1F-42EB-4C07-9FBE-38DB6B872E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C156B1A5-1142-4576-8EAB-D53D9A8AE0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
   <si>
     <t>year</t>
   </si>
@@ -39,7 +42,7 @@
     <t xml:space="preserve">Stanat, P., Schipolowski, S., Schneider, R., Weirich, S., Henschel, S. &amp; Sachse, K. A. (Hrsg.). (2023). *IQB-Bildungstrend 2022: Sprachliche Kompetenzen am Ende der 9. Jahrgangsstufe im dritten Ländervergleich.* Waxmann. https://elibrary.utb.de/doi/book/10.31244/9783830997771 </t>
   </si>
   <si>
-    <t xml:space="preserve">Stanat, P., Schipolowski, S., Mahler, N., Weirich, S. &amp; Henschel, S. (2019). *IQB-Bildungstrend 2018: Mathematische und naturwissenschaftliche Kompetenzen am Ende der Sekundarstufe I im zweiten Ländervergleich.* Waxmann Verlag. https://directory.doabooks.org/handle/20.500.12854/50672 </t>
+    <t>Stanat, P., Schipolowski, S., Gentrup, S., Sachse, K. A., Weirich, S. &amp; Henschel, S. (Hrsg.). (2025). *IQB-Bildungstrend 2024. Mathematische und naturwissenschaftliche Kompetenzen am Ende der 9. Jahrgangsstufe im dritten Ländervergleich.* Waxmann.</t>
   </si>
 </sst>
 </file>
@@ -79,7 +82,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -357,13 +360,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="155.59765625" customWidth="1"/>
+    <col min="2" max="2" width="155.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -371,7 +374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2008</v>
       </c>
@@ -379,7 +382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2009</v>
       </c>
@@ -387,7 +390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2011</v>
       </c>
@@ -395,7 +398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2012</v>
       </c>
@@ -403,7 +406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -411,7 +414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -419,7 +422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2018</v>
       </c>
@@ -427,7 +430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2021</v>
       </c>
@@ -435,12 +438,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2022</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/text_elements/BT_Quellenangaben.xlsx
+++ b/inst/extdata/text_elements/BT_Quellenangaben.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eat\BT-ShinyApp\inst\extdata\text_elements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alina\Desktop\IQB\BT-ShinyApp\inst\extdata\text_elements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C156B1A5-1142-4576-8EAB-D53D9A8AE0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF129C2-AF24-4C74-9BB1-94E47E11BABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -42,7 +39,7 @@
     <t xml:space="preserve">Stanat, P., Schipolowski, S., Schneider, R., Weirich, S., Henschel, S. &amp; Sachse, K. A. (Hrsg.). (2023). *IQB-Bildungstrend 2022: Sprachliche Kompetenzen am Ende der 9. Jahrgangsstufe im dritten Ländervergleich.* Waxmann. https://elibrary.utb.de/doi/book/10.31244/9783830997771 </t>
   </si>
   <si>
-    <t>Stanat, P., Schipolowski, S., Gentrup, S., Sachse, K. A., Weirich, S. &amp; Henschel, S. (Hrsg.). (2025). *IQB-Bildungstrend 2024. Mathematische und naturwissenschaftliche Kompetenzen am Ende der 9. Jahrgangsstufe im dritten Ländervergleich.* Waxmann.</t>
+    <t>Stanat, P., Schipolowski, S., Gentrup, S., Sachse, K. A., Weirich, S. &amp; Henschel, S. (Hrsg.). (2025). *IQB-Bildungstrend 2024: Mathematische und naturwissenschaftliche Kompetenzen am Ende der 9. Jahrgangsstufe im dritten Ländervergleich.* Waxmann.</t>
   </si>
 </sst>
 </file>
@@ -82,7 +79,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -361,12 +358,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="155.5703125" customWidth="1"/>
+    <col min="2" max="2" width="155.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -374,7 +371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2008</v>
       </c>
@@ -382,7 +379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2009</v>
       </c>
@@ -390,7 +387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2011</v>
       </c>
@@ -398,7 +395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2012</v>
       </c>
@@ -406,7 +403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -414,7 +411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -422,7 +419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2018</v>
       </c>
@@ -430,7 +427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2021</v>
       </c>
@@ -438,7 +435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2022</v>
       </c>
@@ -446,7 +443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2024</v>
       </c>
